--- a/processed_data/hard_data_exports/hunt_tables/2026/2026_MOOSE_BULL.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/2026_MOOSE_BULL.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_moose_bull" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2026_moose_bull" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026_moose_bull'!$A$3:$J$30</definedName>
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -614,6 +614,26 @@
           <t>Total</t>
         </is>
       </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Harvest Prior Year</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>Harvest Success (Prior Year %)</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Average Harvest Age (Prior Year)</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>Average Days Hunted (Prior Year)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -654,6 +674,20 @@
       <c r="H4" s="6" t="inlineStr"/>
       <c r="I4" s="6" t="inlineStr"/>
       <c r="J4" s="6" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -706,6 +740,20 @@
           <t>17</t>
         </is>
       </c>
+      <c r="K5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -758,6 +806,20 @@
           <t>4</t>
         </is>
       </c>
+      <c r="K6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -810,6 +872,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -862,6 +938,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -914,6 +1004,20 @@
           <t>6</t>
         </is>
       </c>
+      <c r="K9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -966,6 +1070,20 @@
           <t>6</t>
         </is>
       </c>
+      <c r="K10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -1018,6 +1136,20 @@
           <t>23</t>
         </is>
       </c>
+      <c r="K11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1070,6 +1202,20 @@
           <t>8</t>
         </is>
       </c>
+      <c r="K12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
@@ -1122,6 +1268,20 @@
           <t>7</t>
         </is>
       </c>
+      <c r="K13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -1174,6 +1334,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
@@ -1226,6 +1400,20 @@
           <t>6</t>
         </is>
       </c>
+      <c r="K15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -1278,6 +1466,20 @@
           <t>22</t>
         </is>
       </c>
+      <c r="K16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
@@ -1330,6 +1532,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -1382,6 +1598,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K18" t="n">
+        <v>2021</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
@@ -1434,6 +1656,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -1486,6 +1722,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
@@ -1538,6 +1788,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -1590,6 +1854,20 @@
           <t>4</t>
         </is>
       </c>
+      <c r="K22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
@@ -1642,6 +1920,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
@@ -1694,6 +1986,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K24" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
@@ -1746,6 +2052,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -1798,6 +2118,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K26" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
@@ -1850,6 +2184,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -1902,6 +2250,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K28" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
@@ -1954,6 +2316,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
@@ -2004,6 +2380,20 @@
       <c r="J30" s="6" t="inlineStr">
         <is>
           <t>3</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
